--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9343"/>
+  <dimension ref="A1:B9344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75232,6 +75232,14 @@
       </c>
       <c r="B9343" t="inlineStr"/>
     </row>
+    <row r="9344">
+      <c r="A9344" t="inlineStr">
+        <is>
+          <t>VDC (Signal)</t>
+        </is>
+      </c>
+      <c r="B9344" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9344"/>
+  <dimension ref="A1:B9345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75240,6 +75240,14 @@
       </c>
       <c r="B9344" t="inlineStr"/>
     </row>
+    <row r="9345">
+      <c r="A9345" t="inlineStr">
+        <is>
+          <t>W (19400mW to 25900mW)</t>
+        </is>
+      </c>
+      <c r="B9345" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9345"/>
+  <dimension ref="A1:B9346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75248,6 +75248,14 @@
       </c>
       <c r="B9345" t="inlineStr"/>
     </row>
+    <row r="9346">
+      <c r="A9346" t="inlineStr">
+        <is>
+          <t>m (588nm to 598nm)</t>
+        </is>
+      </c>
+      <c r="B9346" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9346"/>
+  <dimension ref="A1:B9349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75256,6 +75256,30 @@
       </c>
       <c r="B9346" t="inlineStr"/>
     </row>
+    <row r="9347">
+      <c r="A9347" t="inlineStr">
+        <is>
+          <t>m (455nm to 465nm)</t>
+        </is>
+      </c>
+      <c r="B9347" t="inlineStr"/>
+    </row>
+    <row r="9348">
+      <c r="A9348" t="inlineStr">
+        <is>
+          <t>m (405nm to 415nm)</t>
+        </is>
+      </c>
+      <c r="B9348" t="inlineStr"/>
+    </row>
+    <row r="9349">
+      <c r="A9349" t="inlineStr">
+        <is>
+          <t>m (626nm to 638nm)</t>
+        </is>
+      </c>
+      <c r="B9349" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9349"/>
+  <dimension ref="A1:B9352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75280,6 +75280,30 @@
       </c>
       <c r="B9349" t="inlineStr"/>
     </row>
+    <row r="9350">
+      <c r="A9350" t="inlineStr">
+        <is>
+          <t>lm (920lm to 1040lm)</t>
+        </is>
+      </c>
+      <c r="B9350" t="inlineStr"/>
+    </row>
+    <row r="9351">
+      <c r="A9351" t="inlineStr">
+        <is>
+          <t>K (5180K to 6250K)</t>
+        </is>
+      </c>
+      <c r="B9351" t="inlineStr"/>
+    </row>
+    <row r="9352">
+      <c r="A9352" t="inlineStr">
+        <is>
+          <t>K (2850K to 3800K)</t>
+        </is>
+      </c>
+      <c r="B9352" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9352"/>
+  <dimension ref="A1:B9353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75304,6 +75304,14 @@
       </c>
       <c r="B9352" t="inlineStr"/>
     </row>
+    <row r="9353">
+      <c r="A9353" t="inlineStr">
+        <is>
+          <t>mA (DC) per Contact</t>
+        </is>
+      </c>
+      <c r="B9353" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9353"/>
+  <dimension ref="A1:B9352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75304,14 +75304,6 @@
       </c>
       <c r="B9352" t="inlineStr"/>
     </row>
-    <row r="9353">
-      <c r="A9353" t="inlineStr">
-        <is>
-          <t>mA (DC) per Contact</t>
-        </is>
-      </c>
-      <c r="B9353" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9352"/>
+  <dimension ref="A1:B9353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75304,6 +75304,14 @@
       </c>
       <c r="B9352" t="inlineStr"/>
     </row>
+    <row r="9353">
+      <c r="A9353" t="inlineStr">
+        <is>
+          <t>A (DC) per Contact</t>
+        </is>
+      </c>
+      <c r="B9353" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9353"/>
+  <dimension ref="A1:B9356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75312,6 +75312,30 @@
       </c>
       <c r="B9353" t="inlineStr"/>
     </row>
+    <row r="9354">
+      <c r="A9354" t="inlineStr">
+        <is>
+          <t>m (621nm to 645nm)</t>
+        </is>
+      </c>
+      <c r="B9354" t="inlineStr"/>
+    </row>
+    <row r="9355">
+      <c r="A9355" t="inlineStr">
+        <is>
+          <t>m (520nm to 550nm)</t>
+        </is>
+      </c>
+      <c r="B9355" t="inlineStr"/>
+    </row>
+    <row r="9356">
+      <c r="A9356" t="inlineStr">
+        <is>
+          <t>lm (140lm to 250lm)</t>
+        </is>
+      </c>
+      <c r="B9356" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9356"/>
+  <dimension ref="A1:B9357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75336,6 +75336,14 @@
       </c>
       <c r="B9356" t="inlineStr"/>
     </row>
+    <row r="9357">
+      <c r="A9357" t="inlineStr">
+        <is>
+          <t>°C (±10°C)</t>
+        </is>
+      </c>
+      <c r="B9357" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9357"/>
+  <dimension ref="A1:B9360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75344,6 +75344,30 @@
       </c>
       <c r="B9357" t="inlineStr"/>
     </row>
+    <row r="9358">
+      <c r="A9358" t="inlineStr">
+        <is>
+          <t>lm (10lm to 49lm)</t>
+        </is>
+      </c>
+      <c r="B9358" t="inlineStr"/>
+    </row>
+    <row r="9359">
+      <c r="A9359" t="inlineStr">
+        <is>
+          <t>m (609nm to 624nm)</t>
+        </is>
+      </c>
+      <c r="B9359" t="inlineStr"/>
+    </row>
+    <row r="9360">
+      <c r="A9360" t="inlineStr">
+        <is>
+          <t>m (567nm to 575nm)</t>
+        </is>
+      </c>
+      <c r="B9360" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9360"/>
+  <dimension ref="A1:B9365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75368,6 +75368,46 @@
       </c>
       <c r="B9360" t="inlineStr"/>
     </row>
+    <row r="9361">
+      <c r="A9361" t="inlineStr">
+        <is>
+          <t>lm (9lm to 15lm)</t>
+        </is>
+      </c>
+      <c r="B9361" t="inlineStr"/>
+    </row>
+    <row r="9362">
+      <c r="A9362" t="inlineStr">
+        <is>
+          <t>lm (182lm to 187lm)</t>
+        </is>
+      </c>
+      <c r="B9362" t="inlineStr"/>
+    </row>
+    <row r="9363">
+      <c r="A9363" t="inlineStr">
+        <is>
+          <t>lm (80lm to 110lm)</t>
+        </is>
+      </c>
+      <c r="B9363" t="inlineStr"/>
+    </row>
+    <row r="9364">
+      <c r="A9364" t="inlineStr">
+        <is>
+          <t>lm (271lm to 327lm)</t>
+        </is>
+      </c>
+      <c r="B9364" t="inlineStr"/>
+    </row>
+    <row r="9365">
+      <c r="A9365" t="inlineStr">
+        <is>
+          <t>lm (78lm to 82lm)</t>
+        </is>
+      </c>
+      <c r="B9365" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9365"/>
+  <dimension ref="A1:B9367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75408,6 +75408,22 @@
       </c>
       <c r="B9365" t="inlineStr"/>
     </row>
+    <row r="9366">
+      <c r="A9366" t="inlineStr">
+        <is>
+          <t>m (450nm to 460nm)</t>
+        </is>
+      </c>
+      <c r="B9366" t="inlineStr"/>
+    </row>
+    <row r="9367">
+      <c r="A9367" t="inlineStr">
+        <is>
+          <t>lm (45lm to 70lm)</t>
+        </is>
+      </c>
+      <c r="B9367" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9367"/>
+  <dimension ref="A1:B9369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75424,6 +75424,22 @@
       </c>
       <c r="B9367" t="inlineStr"/>
     </row>
+    <row r="9368">
+      <c r="A9368" t="inlineStr">
+        <is>
+          <t>W (1250mW to 2400mW)</t>
+        </is>
+      </c>
+      <c r="B9368" t="inlineStr"/>
+    </row>
+    <row r="9369">
+      <c r="A9369" t="inlineStr">
+        <is>
+          <t>W (1100mW to 2000mW)</t>
+        </is>
+      </c>
+      <c r="B9369" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9369"/>
+  <dimension ref="A1:B9370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75440,6 +75440,14 @@
       </c>
       <c r="B9369" t="inlineStr"/>
     </row>
+    <row r="9370">
+      <c r="A9370" t="inlineStr">
+        <is>
+          <t>V (5V, 8V)</t>
+        </is>
+      </c>
+      <c r="B9370" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9370"/>
+  <dimension ref="A1:B9377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75448,6 +75448,62 @@
       </c>
       <c r="B9370" t="inlineStr"/>
     </row>
+    <row r="9371">
+      <c r="A9371" t="inlineStr">
+        <is>
+          <t>lm (186lm to 206lm)</t>
+        </is>
+      </c>
+      <c r="B9371" t="inlineStr"/>
+    </row>
+    <row r="9372">
+      <c r="A9372" t="inlineStr">
+        <is>
+          <t>lm (158lm to 178lm)</t>
+        </is>
+      </c>
+      <c r="B9372" t="inlineStr"/>
+    </row>
+    <row r="9373">
+      <c r="A9373" t="inlineStr">
+        <is>
+          <t>lm (175lm to 195lm)</t>
+        </is>
+      </c>
+      <c r="B9373" t="inlineStr"/>
+    </row>
+    <row r="9374">
+      <c r="A9374" t="inlineStr">
+        <is>
+          <t>lm (195lm to 215lm)</t>
+        </is>
+      </c>
+      <c r="B9374" t="inlineStr"/>
+    </row>
+    <row r="9375">
+      <c r="A9375" t="inlineStr">
+        <is>
+          <t>lm (176lm to 196lm)</t>
+        </is>
+      </c>
+      <c r="B9375" t="inlineStr"/>
+    </row>
+    <row r="9376">
+      <c r="A9376" t="inlineStr">
+        <is>
+          <t>lm (193lm to 213lm)</t>
+        </is>
+      </c>
+      <c r="B9376" t="inlineStr"/>
+    </row>
+    <row r="9377">
+      <c r="A9377" t="inlineStr">
+        <is>
+          <t>lm (196lm to 216lm)</t>
+        </is>
+      </c>
+      <c r="B9377" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9377"/>
+  <dimension ref="A1:B9378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75504,6 +75504,14 @@
       </c>
       <c r="B9377" t="inlineStr"/>
     </row>
+    <row r="9378">
+      <c r="A9378" t="inlineStr">
+        <is>
+          <t>lm (182lm to 192lm)</t>
+        </is>
+      </c>
+      <c r="B9378" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9378"/>
+  <dimension ref="A1:B9383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75512,6 +75512,46 @@
       </c>
       <c r="B9378" t="inlineStr"/>
     </row>
+    <row r="9379">
+      <c r="A9379" t="inlineStr">
+        <is>
+          <t>lm (205lm to 225lm)</t>
+        </is>
+      </c>
+      <c r="B9379" t="inlineStr"/>
+    </row>
+    <row r="9380">
+      <c r="A9380" t="inlineStr">
+        <is>
+          <t>lm (248lm to 268lm)</t>
+        </is>
+      </c>
+      <c r="B9380" t="inlineStr"/>
+    </row>
+    <row r="9381">
+      <c r="A9381" t="inlineStr">
+        <is>
+          <t>lm (255lm to 275lm)</t>
+        </is>
+      </c>
+      <c r="B9381" t="inlineStr"/>
+    </row>
+    <row r="9382">
+      <c r="A9382" t="inlineStr">
+        <is>
+          <t>lm (247lm to 267lm)</t>
+        </is>
+      </c>
+      <c r="B9382" t="inlineStr"/>
+    </row>
+    <row r="9383">
+      <c r="A9383" t="inlineStr">
+        <is>
+          <t>lm (230lm to 250lm)</t>
+        </is>
+      </c>
+      <c r="B9383" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9383"/>
+  <dimension ref="A1:B9399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75552,6 +75552,134 @@
       </c>
       <c r="B9383" t="inlineStr"/>
     </row>
+    <row r="9384">
+      <c r="A9384" t="inlineStr">
+        <is>
+          <t>lm (22lm to 32lm)</t>
+        </is>
+      </c>
+      <c r="B9384" t="inlineStr"/>
+    </row>
+    <row r="9385">
+      <c r="A9385" t="inlineStr">
+        <is>
+          <t>lm (1150lm to 1300lm)</t>
+        </is>
+      </c>
+      <c r="B9385" t="inlineStr"/>
+    </row>
+    <row r="9386">
+      <c r="A9386" t="inlineStr">
+        <is>
+          <t>lm (14lm to 17lm)</t>
+        </is>
+      </c>
+      <c r="B9386" t="inlineStr"/>
+    </row>
+    <row r="9387">
+      <c r="A9387" t="inlineStr">
+        <is>
+          <t>lm (11lm to 12lm)</t>
+        </is>
+      </c>
+      <c r="B9387" t="inlineStr"/>
+    </row>
+    <row r="9388">
+      <c r="A9388" t="inlineStr">
+        <is>
+          <t>lm (400lm to 475lm)</t>
+        </is>
+      </c>
+      <c r="B9388" t="inlineStr"/>
+    </row>
+    <row r="9389">
+      <c r="A9389" t="inlineStr">
+        <is>
+          <t>lm (850lm to 950lm)</t>
+        </is>
+      </c>
+      <c r="B9389" t="inlineStr"/>
+    </row>
+    <row r="9390">
+      <c r="A9390" t="inlineStr">
+        <is>
+          <t>lm (19lm to 28lm)</t>
+        </is>
+      </c>
+      <c r="B9390" t="inlineStr"/>
+    </row>
+    <row r="9391">
+      <c r="A9391" t="inlineStr">
+        <is>
+          <t>m (627nm to 636nm)</t>
+        </is>
+      </c>
+      <c r="B9391" t="inlineStr"/>
+    </row>
+    <row r="9392">
+      <c r="A9392" t="inlineStr">
+        <is>
+          <t>lm (13lm to 19lm)</t>
+        </is>
+      </c>
+      <c r="B9392" t="inlineStr"/>
+    </row>
+    <row r="9393">
+      <c r="A9393" t="inlineStr">
+        <is>
+          <t>lm (4lm to 9lm)</t>
+        </is>
+      </c>
+      <c r="B9393" t="inlineStr"/>
+    </row>
+    <row r="9394">
+      <c r="A9394" t="inlineStr">
+        <is>
+          <t>lm (39lm to 59lm)</t>
+        </is>
+      </c>
+      <c r="B9394" t="inlineStr"/>
+    </row>
+    <row r="9395">
+      <c r="A9395" t="inlineStr">
+        <is>
+          <t>lm (34lm to 59lm)</t>
+        </is>
+      </c>
+      <c r="B9395" t="inlineStr"/>
+    </row>
+    <row r="9396">
+      <c r="A9396" t="inlineStr">
+        <is>
+          <t>lm (138lm to 170lm)</t>
+        </is>
+      </c>
+      <c r="B9396" t="inlineStr"/>
+    </row>
+    <row r="9397">
+      <c r="A9397" t="inlineStr">
+        <is>
+          <t>m (518nm to 539nm)</t>
+        </is>
+      </c>
+      <c r="B9397" t="inlineStr"/>
+    </row>
+    <row r="9398">
+      <c r="A9398" t="inlineStr">
+        <is>
+          <t>lm (62lm to 90lm)</t>
+        </is>
+      </c>
+      <c r="B9398" t="inlineStr"/>
+    </row>
+    <row r="9399">
+      <c r="A9399" t="inlineStr">
+        <is>
+          <t>m (586nm to 595nm)</t>
+        </is>
+      </c>
+      <c r="B9399" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
